--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\ClaimPoints\ClaimPoints\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162C2F13-211E-4F45-B193-C002E30A4EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CA2734-D488-43F9-A48D-F8BEA748DF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -28,9 +28,6 @@
     <t>TEST_DESC</t>
   </si>
   <si>
-    <t>COMPANY_NAME</t>
-  </si>
-  <si>
     <t>EXPECTED_RESULT</t>
   </si>
   <si>
@@ -49,12 +46,6 @@
     <t>MODULE_NAME</t>
   </si>
   <si>
-    <t>2601000018</t>
-  </si>
-  <si>
-    <t>ClaimPoints</t>
-  </si>
-  <si>
     <t>ClaimInformationPageTest_01</t>
   </si>
   <si>
@@ -131,6 +122,12 @@
   </si>
   <si>
     <t>ClaimInformationPageTest_13</t>
+  </si>
+  <si>
+    <t>2602000005</t>
+  </si>
+  <si>
+    <t>02_ClaimPoints</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -1067,18 +1064,17 @@
     <col min="3" max="3" width="25.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="128.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="57.1796875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.90625" style="2"/>
+    <col min="6" max="6" width="57.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -1087,253 +1083,237 @@
         <v>1</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
@@ -8,19 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CA2734-D488-43F9-A48D-F8BEA748DF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01269EA0-1E00-49A4-8388-704DCEF0F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -49,45 +63,6 @@
     <t>ClaimInformationPageTest_01</t>
   </si>
   <si>
-    <t>Veriffy if we select cement category product then claim information fields should work as nonmandatory</t>
-  </si>
-  <si>
-    <t>Veriffy if we select TMT category product then claim information fields should work as mandatory</t>
-  </si>
-  <si>
-    <t>Verify claim information field name  for Cement category</t>
-  </si>
-  <si>
-    <t>Verify claim information field name for TMT category</t>
-  </si>
-  <si>
-    <t>Verify claim information field name for Tiles category</t>
-  </si>
-  <si>
-    <t>If we select 1 product from non mandory fields category &amp; 1 product from Mandatory field product then on claim information field should be work as mandatory</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Keep Cutomer Name field blank verify  warning msg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Keep Cutomer mobile number field  blank verify  warning msg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Enter Invalid  Cutomer mobile number verify  warning msg</t>
-  </si>
-  <si>
-    <t>Verify material photo warning msg</t>
-  </si>
-  <si>
-    <t>Verify site address field warning msg</t>
-  </si>
-  <si>
-    <t>Verify site photo warning msg</t>
-  </si>
-  <si>
-    <t>After fill all mandory fields and click on submit button then submit claim pop-up should be display.</t>
-  </si>
-  <si>
     <t>ClaimInformationPageTest_02</t>
   </si>
   <si>
@@ -128,13 +103,985 @@
   </si>
   <si>
     <t>02_ClaimPoints</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify if we select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>TMT category (Fortune TMT)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  product then </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>claim information</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> fields should work as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>mandatory</t>
+    </r>
+  </si>
+  <si>
+    <t>CUTOMER_NAME</t>
+  </si>
+  <si>
+    <t>CUSTOMER_MOBILE</t>
+  </si>
+  <si>
+    <t>SITE_ADDRESS</t>
+  </si>
+  <si>
+    <t>CATEGORY_NAME</t>
+  </si>
+  <si>
+    <t>BRAND_NAME</t>
+  </si>
+  <si>
+    <t>PRODUCT_NAME</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>PRODUCT_REMARK</t>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Ambuja Cement</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Ambj001</t>
+  </si>
+  <si>
+    <t>openclaimpointsmenu
+myclaims_clickonfabbutton
+dealerlist_clickonradiobutton
+dealer_enterinvno
+dealer_clickonimagecaptureicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+dealer_clickonnextbutton
+category_selectcategory
+category_selectbrand
+category_enterproductname_insearchfield
+hidekeyboard
+category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+claiminfo_clikon_submitbtn
+verify_claiminfo_alertbox_title</t>
+  </si>
+  <si>
+    <t>Submit Claim</t>
+  </si>
+  <si>
+    <t>TMT</t>
+  </si>
+  <si>
+    <t>Fortune TMT</t>
+  </si>
+  <si>
+    <t>PROD013</t>
+  </si>
+  <si>
+    <t>Please enter customer mobile No.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify if we select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cement category product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> then</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> claim information</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> fields should work as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nonmandatory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Adani, Ambuja &amp;Wonder Cement group).</t>
+    </r>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <r>
+      <t>If we select</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1 produc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t from</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> non mandory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fields </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 produc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">t from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mandatory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field product then on claim information field should be work as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mandatory</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>claim information field name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cement category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( Company Name -Adani, Ambuja &amp;Wonder Cement ).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>claim information field name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TMT category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Company Name - Fortune TMT)</t>
+    </r>
+  </si>
+  <si>
+    <t>ClaimInformationPageTest_14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify  for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TMT category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - (Company name - J</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>indal Panther</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Claim fields should not be show</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Jindal Panther</t>
+  </si>
+  <si>
+    <t>Product Added</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>claim information field name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tiles category</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>claim information field name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TMT category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Company Name - Jindal Stainless Limited)</t>
+    </r>
+  </si>
+  <si>
+    <t>ClaimInformationPageTest_15</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Keep </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cutomer Name field blank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> verify  warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Keep </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cutomer mobile number field  blank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> verify  warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Invalid  Cutomer mobile number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> verify  warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>material photo warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>site address field warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> site photo warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>After</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fill all mandory fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and click on submit button then </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>submit claim pop-up should be display</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>CUSTOMER_DETAILS_FIELDS</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Jindal Stainless</t>
+  </si>
+  <si>
+    <t>Tiles</t>
+  </si>
+  <si>
+    <t>Vitrified</t>
+  </si>
+  <si>
+    <t>Customer Name,Customer Mobile No</t>
+  </si>
+  <si>
+    <t>Prasad Sinha</t>
+  </si>
+  <si>
+    <t>6444444</t>
+  </si>
+  <si>
+    <t>claiminfo_enter_customername
+hidekeyboard
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>claiminfo_enter_customermobileno
+hidekeyboard
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>Please enter valid mobile number</t>
+  </si>
+  <si>
+    <t>4567896543</t>
+  </si>
+  <si>
+    <t>select or capture all mandatory material Photos</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_materialproductimageicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>Please enter site address</t>
+  </si>
+  <si>
+    <t>Mayur colony, kothrud, Pune 411038</t>
+  </si>
+  <si>
+    <t>claiminfo_enter_siteaddress
+hidekeyboard
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>Please select or capture site photo</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_alertbox_nobtn
+claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clear_searchfield
+category_selectcategory
+category_selectbrand
+category_enterproductname_insearchfield
+hidekeyboard
+category_enterqty
+hidekeyboard
+category_select_product_diameter
+category_clickon_addtocart_btn
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_select_product_size
+category_clickon_addtocart_btn
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verify_claiminfo_customerdetailsfields</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_select_product_diameter
+category_clickon_addtocart_btn
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verify_claiminfo_customerdetailsfields</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verify_claiminfo_customerdetailsfields</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_clear_searchfield
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_selecttmtcategory
+category_selectfortunrtmtbrand
+category_enterqty
+hidekeyboard
+category_select_product_diameter
+category_clickon_addtocart_btn
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_enter_productremark
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verify_claiminfo_alertbox_title</t>
+  </si>
+  <si>
+    <t>*Customer Name,*Customer Mobile No,*Site Address,*Site photo,Invoice details,*Invoice photo,Material Photo</t>
+  </si>
+  <si>
+    <t>Customer Name,Customer Mobile No,Site Address,Site photo,Invoice details,Invoice photo,Material Photo</t>
+  </si>
+  <si>
+    <t>*Customer Name,*Customer Mobile No,Site Address,Site photo,Invoice details,Invoice photo,Material Photo</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_alertbox_nobtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verify_claiminfo_customerdetailsfields</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_select_product_diameter
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>Kothrud</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_sitephotoicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_submitbtn
+verify_claiminfo_alertbox_title
+claiminfo_clikon_alertbox_nobtn
+claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+clickonbackarrow
+dealerlist_clickoncrossicon
+navigatebacktodashboardpage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,6 +1227,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">
@@ -669,7 +1623,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -680,6 +1634,9 @@
     <xf numFmtId="49" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1056,20 +2013,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultColWidth="94.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="128.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.90625" style="2"/>
+    <col min="4" max="4" width="93" style="2" customWidth="1"/>
+    <col min="5" max="5" width="36.6328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="11" width="95.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="94.36328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -1086,238 +2052,1233 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="290" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="261" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="4" spans="1:16" ht="304.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="D4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
+    <row r="5" spans="1:16" ht="203" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="D5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
+    <row r="6" spans="1:16" ht="174" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1" t="s">
+    <row r="7" spans="1:16" ht="203" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    <row r="8" spans="1:16" ht="203" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
+    <row r="9" spans="1:16" ht="174" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
+    <row r="10" spans="1:16" ht="232" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="1" t="s">
+    <row r="11" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="174" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94275DA9-BB27-45DB-906E-55DB38AB6FED}">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultColWidth="94.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93" style="2" customWidth="1"/>
+    <col min="5" max="5" width="36.6328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="11" width="95.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="94.36328125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="290" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="261" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="304.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="203" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="174" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="203" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="203" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="174" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="232" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="174" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01269EA0-1E00-49A4-8388-704DCEF0F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7FD917-CB26-441E-8C76-F2BBC2FFF47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="91">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -877,12 +877,6 @@
 verify_warningmsg</t>
   </si>
   <si>
-    <t>claiminfo_enter_customermobileno
-hidekeyboard
-claiminfo_clikon_submitbtn
-verify_warningmsg</t>
-  </si>
-  <si>
     <t>Please enter valid mobile number</t>
   </si>
   <si>
@@ -892,23 +886,7 @@
     <t>select or capture all mandatory material Photos</t>
   </si>
   <si>
-    <t>claiminfo_clikon_materialproductimageicon
-clickonbrowsefileoption
-selectimageclickonbrowsefileoption
-claiminfo_clikon_submitbtn
-verify_warningmsg</t>
-  </si>
-  <si>
     <t>Please enter site address</t>
-  </si>
-  <si>
-    <t>Mayur colony, kothrud, Pune 411038</t>
-  </si>
-  <si>
-    <t>claiminfo_enter_siteaddress
-hidekeyboard
-claiminfo_clikon_submitbtn
-verify_warningmsg</t>
   </si>
   <si>
     <t>Please select or capture site photo</t>
@@ -1075,6 +1053,28 @@
 clickonbackarrow
 dealerlist_clickoncrossicon
 navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>waitforsnackbardisappear
+claiminfo_enter_customermobileno
+hidekeyboard
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>waitforsnackbardisappear
+claiminfo_clikon_materialproductimageicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>waitforsnackbardisappear
+claiminfo_enter_siteaddress
+hidekeyboard
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2139,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>38</v>
@@ -2179,7 +2179,7 @@
         <v>44</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
@@ -2217,7 +2217,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>38</v>
@@ -2257,7 +2257,7 @@
         <v>45</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>32</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2297,7 +2297,7 @@
         <v>46</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>38</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2337,7 +2337,7 @@
         <v>52</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -2377,7 +2377,7 @@
         <v>51</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>64</v>
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>38</v>
@@ -2475,7 +2475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>56</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -2503,13 +2503,13 @@
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>57</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2533,17 +2533,17 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>58</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -2569,13 +2569,13 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>59</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -2600,10 +2600,10 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>5</v>
@@ -2623,7 +2623,7 @@
         <v>60</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -2776,7 +2776,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>38</v>
@@ -2816,7 +2816,7 @@
         <v>44</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
@@ -2854,7 +2854,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>38</v>
@@ -2894,7 +2894,7 @@
         <v>45</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>32</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>38</v>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2974,7 +2974,7 @@
         <v>52</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -3014,7 +3014,7 @@
         <v>51</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>64</v>
@@ -3054,7 +3054,7 @@
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>38</v>
@@ -3112,7 +3112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>56</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -3140,13 +3140,13 @@
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>57</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -3170,17 +3170,17 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>58</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -3206,13 +3206,13 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>59</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3237,10 +3237,10 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>5</v>
@@ -3260,7 +3260,7 @@
         <v>60</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7FD917-CB26-441E-8C76-F2BBC2FFF47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1FAEFC-8B51-4FD7-B721-1CE49DE2CF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="94">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -185,13 +185,7 @@
     <t>Cement</t>
   </si>
   <si>
-    <t>Ambuja Cement</t>
-  </si>
-  <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>Ambj001</t>
   </si>
   <si>
     <t>openclaimpointsmenu
@@ -221,12 +215,6 @@
     <t>TMT</t>
   </si>
   <si>
-    <t>Fortune TMT</t>
-  </si>
-  <si>
-    <t>PROD013</t>
-  </si>
-  <si>
     <t>Please enter customer mobile No.</t>
   </si>
   <si>
@@ -581,9 +569,6 @@
     </r>
   </si>
   <si>
-    <t>Jindal Panther</t>
-  </si>
-  <si>
     <t>Product Added</t>
   </si>
   <si>
@@ -620,7 +605,98 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Tiles category</t>
+      <t>TMT category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Company Name - Jindal Stainless Limited)</t>
+    </r>
+  </si>
+  <si>
+    <t>ClaimInformationPageTest_15</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Keep </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cutomer Name field blank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> verify  warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Keep </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cutomer mobile number field  blank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> verify  warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Invalid  Cutomer mobile number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> verify  warning msg</t>
     </r>
   </si>
   <si>
@@ -636,17 +712,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>claim information field name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for </t>
+      <t>material photo warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
     </r>
     <r>
       <rPr>
@@ -657,25 +728,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>TMT category</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Company Name - Jindal Stainless Limited)</t>
-    </r>
-  </si>
-  <si>
-    <t>ClaimInformationPageTest_15</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Keep </t>
+      <t>site address field warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify</t>
     </r>
     <r>
       <rPr>
@@ -686,22 +744,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Cutomer Name field blank</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> verify  warning msg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Keep </t>
+      <t xml:space="preserve"> site photo warning msg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>After</t>
     </r>
     <r>
       <rPr>
@@ -712,22 +760,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Cutomer mobile number field  blank</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> verify  warning msg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Enter </t>
+      <t xml:space="preserve"> fill all mandory fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and click on submit button then </t>
     </r>
     <r>
       <rPr>
@@ -738,101 +781,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Invalid  Cutomer mobile number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> verify  warning msg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>material photo warning msg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>site address field warning msg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> site photo warning msg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>After</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> fill all mandory fields</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and click on submit button then </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>submit claim pop-up should be display</t>
     </r>
     <r>
@@ -853,16 +801,7 @@
     <t>true</t>
   </si>
   <si>
-    <t>Jindal Stainless</t>
-  </si>
-  <si>
     <t>Tiles</t>
-  </si>
-  <si>
-    <t>Vitrified</t>
-  </si>
-  <si>
-    <t>Customer Name,Customer Mobile No</t>
   </si>
   <si>
     <t>Prasad Sinha</t>
@@ -1020,7 +959,128 @@
 verify_claiminfo_customerdetailsfields</t>
   </si>
   <si>
+    <t>Kothrud</t>
+  </si>
+  <si>
+    <t>claiminfo_clikon_sitephotoicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_submitbtn
+verify_claiminfo_alertbox_title
+claiminfo_clikon_alertbox_nobtn
+claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+clickonbackarrow
+dealerlist_clickoncrossicon
+navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>waitforsnackbardisappear
+claiminfo_enter_customermobileno
+hidekeyboard
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>waitforsnackbardisappear
+claiminfo_clikon_materialproductimageicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>waitforsnackbardisappear
+claiminfo_enter_siteaddress
+hidekeyboard
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>APPIUM CEMENT</t>
+  </si>
+  <si>
+    <t>APMCMT0001</t>
+  </si>
+  <si>
+    <t>APPIUM TMT</t>
+  </si>
+  <si>
+    <t>APMTMT0001</t>
+  </si>
+  <si>
+    <t>APPIUM TILES</t>
+  </si>
+  <si>
+    <t>APPIUM Stainless</t>
+  </si>
+  <si>
+    <t>APPIUM Panther</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>claim information field name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tiles category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( Claim fields should not be show))</t>
+    </r>
+  </si>
+  <si>
     <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verify_claiminfo_alertbox_title</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_alertbox_nobtn
 cartdetails_clickon_cancelbtn
 cartdetails_clickon_alertbox_yesbtn
 category_clickon_refreshbtn
@@ -1038,43 +1098,52 @@
 verify_warningmsg</t>
   </si>
   <si>
-    <t>Kothrud</t>
-  </si>
-  <si>
-    <t>claiminfo_clikon_sitephotoicon
-clickonbrowsefileoption
-selectimageclickonbrowsefileoption
-claiminfo_clikon_submitbtn
-verify_claiminfo_alertbox_title
-claiminfo_clikon_alertbox_nobtn
-claiminfo_clikon_cancelbtn
+    <t>claiminfo_clikon_cancelbtn
 cartdetails_clickon_cancelbtn
 cartdetails_clickon_alertbox_yesbtn
-clickonbackarrow
-dealerlist_clickoncrossicon
-navigatebacktodashboardpage</t>
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_enter_productremark
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verify_claiminfo_customerdetailsfields</t>
   </si>
   <si>
     <t>waitforsnackbardisappear
 claiminfo_enter_customermobileno
 hidekeyboard
-claiminfo_clikon_submitbtn
-verify_warningmsg</t>
-  </si>
-  <si>
-    <t>waitforsnackbardisappear
-claiminfo_clikon_materialproductimageicon
-clickonbrowsefileoption
-selectimageclickonbrowsefileoption
-claiminfo_clikon_submitbtn
-verify_warningmsg</t>
-  </si>
-  <si>
-    <t>waitforsnackbardisappear
-claiminfo_enter_siteaddress
-hidekeyboard
-claiminfo_clikon_submitbtn
-verify_warningmsg</t>
+claiminfo_clikon_submitbtn</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>material photo warning msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (non mandatory fo appium TMT)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1236,7 +1305,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1419,6 +1488,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1623,7 +1698,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1637,6 +1712,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="34" borderId="10" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2022,7 +2105,7 @@
     <col min="4" max="4" width="93" style="2" customWidth="1"/>
     <col min="5" max="5" width="36.6328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="2" customWidth="1"/>
@@ -2067,7 +2150,7 @@
         <v>31</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>24</v>
@@ -2096,22 +2179,22 @@
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -2119,7 +2202,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>5</v>
@@ -2139,19 +2222,19 @@
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2159,7 +2242,7 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>5</v>
@@ -2176,20 +2259,20 @@
         <v>10</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2197,7 +2280,7 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>5</v>
@@ -2214,192 +2297,192 @@
         <v>11</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="4" t="s">
-        <v>37</v>
+      <c r="O5" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="174" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:16" s="12" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="D6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6" s="1" t="s">
+      <c r="G6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="203" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:16" s="12" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="12" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="E8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P7" s="1" t="s">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="203" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:16" s="12" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="174" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="1" t="s">
+      <c r="D9" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2414,20 +2497,20 @@
         <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -2435,7 +2518,7 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>5</v>
@@ -2452,10 +2535,10 @@
         <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -2464,12 +2547,12 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>5</v>
@@ -2486,10 +2569,10 @@
         <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -2499,17 +2582,17 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -2520,10 +2603,10 @@
         <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2533,11 +2616,11 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>5</v>
@@ -2554,10 +2637,10 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -2569,7 +2652,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>5</v>
@@ -2583,13 +2666,13 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -2600,10 +2683,10 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>5</v>
@@ -2617,13 +2700,13 @@
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -2635,7 +2718,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>5</v>
@@ -2649,7 +2732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94275DA9-BB27-45DB-906E-55DB38AB6FED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78FFB4BE-9119-4AA8-BD80-966901540198}">
   <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="94.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2659,7 +2742,7 @@
     <col min="4" max="4" width="93" style="2" customWidth="1"/>
     <col min="5" max="5" width="36.6328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="2" customWidth="1"/>
@@ -2704,7 +2787,7 @@
         <v>31</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>24</v>
@@ -2733,22 +2816,22 @@
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -2756,7 +2839,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>5</v>
@@ -2776,19 +2859,19 @@
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2796,7 +2879,7 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>5</v>
@@ -2813,20 +2896,20 @@
         <v>10</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2834,7 +2917,7 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>5</v>
@@ -2851,192 +2934,192 @@
         <v>11</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="4" t="s">
-        <v>37</v>
+      <c r="O5" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="174" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:16" s="12" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="D6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6" s="1" t="s">
+      <c r="G6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="203" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:16" s="12" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="12" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="E8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P7" s="1" t="s">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="203" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:16" s="12" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="174" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="1" t="s">
+      <c r="D9" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3051,20 +3134,20 @@
         <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -3072,7 +3155,7 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>5</v>
@@ -3089,10 +3172,10 @@
         <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -3101,12 +3184,12 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>5</v>
@@ -3123,10 +3206,10 @@
         <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -3136,11 +3219,11 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>5</v>
@@ -3157,10 +3240,10 @@
         <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -3170,11 +3253,11 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>5</v>
@@ -3191,10 +3274,10 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -3206,7 +3289,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>5</v>
@@ -3220,13 +3303,13 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3237,10 +3320,10 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>5</v>
@@ -3254,13 +3337,13 @@
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -3272,7 +3355,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1FAEFC-8B51-4FD7-B721-1CE49DE2CF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8012AC-053E-4FA8-B755-7AD5F8CBB7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="96">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1144,6 +1144,27 @@
       </rPr>
       <t xml:space="preserve"> (non mandatory fo appium TMT)</t>
     </r>
+  </si>
+  <si>
+    <t>claiminfo_clikon_cancelbtn
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_select_product_diameter
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+claiminfo_clikon_submitbtn
+verify_warningmsg</t>
+  </si>
+  <si>
+    <t>Customer Name,Customer Mobile No</t>
   </si>
 </sst>
 </file>
@@ -2462,7 +2483,7 @@
         <v>88</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>57</v>
@@ -2475,7 +2496,9 @@
         <v>39</v>
       </c>
       <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="K9" s="9" t="s">
+        <v>95</v>
+      </c>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
@@ -2500,7 +2523,7 @@
         <v>48</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>36</v>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F93D4-4261-4AB4-AEE6-E9FE5063EC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="TestCases"/>
-    <sheet r:id="rId2" sheetId="2" name="Sheet1"/>
+    <sheet name="TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1114,9 +1120,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1127,7 +1132,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -1143,6 +1148,34 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1153,12 +1186,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070c0"/>
+        <fgColor rgb="FF0070C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1172,16 +1205,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1196,7 +1229,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1208,10 +1241,10 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1241,86 +1274,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1331,10 +1362,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1372,71 +1403,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1464,7 +1495,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1487,11 +1518,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1500,13 +1531,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1516,7 +1547,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1525,7 +1556,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1534,7 +1565,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1542,10 +1573,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1610,32 +1641,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="21" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="22" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="22" width="25.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="22" width="93.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="23" width="36.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="22" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="22" width="15.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="22" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="21" width="4.147857142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="22" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="22" width="95.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="22" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="21" width="17.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="22" width="30.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="22" width="28.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="22" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.7265625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.54296875" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.1796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="95.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row r="1" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1685,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row r="2" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
@@ -1725,7 +1756,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="219.75">
+    <row r="3" spans="1:16" ht="219.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
@@ -1765,7 +1796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="242.25">
+    <row r="4" spans="1:16" ht="242.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
@@ -1803,7 +1834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="163.5">
+    <row r="5" spans="1:16" ht="163.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
@@ -1845,7 +1876,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="141">
+    <row r="6" spans="1:16" ht="141" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>16</v>
       </c>
@@ -1885,7 +1916,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="163.5">
+    <row r="7" spans="1:16" ht="163.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
@@ -1925,7 +1956,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="163.5">
+    <row r="8" spans="1:16" ht="163.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
@@ -1965,7 +1996,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="141">
+    <row r="9" spans="1:16" ht="141" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>16</v>
       </c>
@@ -2005,7 +2036,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="186">
+    <row r="10" spans="1:16" ht="186" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -2043,7 +2074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="51">
+    <row r="11" spans="1:16" ht="51" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -2077,7 +2108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="62.25">
+    <row r="12" spans="1:16" ht="62.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -2111,7 +2142,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row r="13" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>16</v>
       </c>
@@ -2145,7 +2176,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row r="14" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
@@ -2177,7 +2208,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row r="15" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
@@ -2211,7 +2242,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row r="16" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>16</v>
       </c>
@@ -2249,32 +2280,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="21" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="22" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="22" width="25.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="22" width="93.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="23" width="36.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="22" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="22" width="15.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="22" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="21" width="4.147857142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="22" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="22" width="95.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="22" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="21" width="17.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="22" width="30.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="22" width="28.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="22" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.7265625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.54296875" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.1796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="95.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row r="1" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2324,7 +2355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row r="2" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
@@ -2364,7 +2395,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row r="3" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
@@ -2404,7 +2435,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row r="4" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
@@ -2442,7 +2473,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row r="5" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
@@ -2484,7 +2515,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row r="6" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>16</v>
       </c>
@@ -2524,7 +2555,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row r="7" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
@@ -2564,7 +2595,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row r="8" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
@@ -2604,7 +2635,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row r="9" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>16</v>
       </c>
@@ -2642,7 +2673,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row r="10" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -2680,7 +2711,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row r="11" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -2714,7 +2745,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row r="12" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -2748,7 +2779,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row r="13" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>16</v>
       </c>
@@ -2782,7 +2813,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row r="14" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
@@ -2814,7 +2845,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row r="15" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
@@ -2848,7 +2879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row r="16" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>16</v>
       </c>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/04_ClaimInformationPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F93D4-4261-4AB4-AEE6-E9FE5063EC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EABEF51-DFAF-4BE6-9372-4C7BFD9F49E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
